--- a/Module/MainModel/整车CAN20260630_MB分配.xlsx
+++ b/Module/MainModel/整车CAN20260630_MB分配.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12280" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MB分配说明_更新" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5355" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="979">
   <si>
     <r>
       <rPr>
@@ -5744,7 +5744,9 @@
       <c r="D15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F15" s="3" t="s">
         <v>19</v>
       </c>
@@ -5780,7 +5782,9 @@
       <c r="D16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F16" s="3" t="s">
         <v>19</v>
       </c>
@@ -5816,7 +5820,9 @@
       <c r="D17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
@@ -5852,7 +5858,9 @@
       <c r="D18" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F18" s="3" t="s">
         <v>122</v>
       </c>
@@ -5888,7 +5896,9 @@
       <c r="D19" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F19" s="3" t="s">
         <v>94</v>
       </c>
@@ -5924,7 +5934,9 @@
       <c r="D20" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F20" s="3" t="s">
         <v>129</v>
       </c>
@@ -5960,7 +5972,9 @@
       <c r="D21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F21" s="3" t="s">
         <v>19</v>
       </c>
@@ -5996,7 +6010,9 @@
       <c r="D22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F22" s="3" t="s">
         <v>94</v>
       </c>
@@ -6032,7 +6048,9 @@
       <c r="D23" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F23" s="3" t="s">
         <v>129</v>
       </c>
@@ -6068,7 +6086,9 @@
       <c r="D24" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
       </c>
@@ -6104,7 +6124,9 @@
       <c r="D25" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F25" s="3" t="s">
         <v>19</v>
       </c>
@@ -6292,7 +6314,9 @@
       <c r="D30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F30" s="3" t="s">
         <v>19</v>
       </c>
@@ -6328,7 +6352,9 @@
       <c r="D31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F31" s="3" t="s">
         <v>19</v>
       </c>
@@ -6364,7 +6390,9 @@
       <c r="D32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F32" s="3" t="s">
         <v>94</v>
       </c>
@@ -6400,7 +6428,9 @@
       <c r="D33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F33" s="3" t="s">
         <v>94</v>
       </c>
@@ -6436,7 +6466,9 @@
       <c r="D34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="F34" s="3" t="s">
         <v>19</v>
       </c>

--- a/Module/MainModel/整车CAN20260630_MB分配.xlsx
+++ b/Module/MainModel/整车CAN20260630_MB分配.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VCU\VCU_SL_ZhengZhou\ZT2\Module\MainModel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MB分配说明_更新" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="982">
   <si>
     <r>
       <rPr>
@@ -55,6 +60,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>4</t>
     </r>
     <r>
@@ -490,10 +500,10 @@
     <t>未受本次BMS注释影响；原MB21</t>
   </si>
   <si>
-    <t>TWV</t>
-  </si>
-  <si>
-    <t>0x18FF243B</t>
+    <t>TWV_VCU</t>
+  </si>
+  <si>
+    <t>0x18FD20B0</t>
   </si>
   <si>
     <t>未受本次BMS注释影响；原MB22</t>
@@ -577,7 +587,7 @@
     <t>VCU_TWV</t>
   </si>
   <si>
-    <t>0x18FF25EF</t>
+    <t>0x0cfd6720</t>
   </si>
   <si>
     <t>未受本次BMS注释影响；原MB31</t>
@@ -2732,6 +2742,12 @@
     <t>ISG MCU STATUS 1</t>
   </si>
   <si>
+    <t>TWV</t>
+  </si>
+  <si>
+    <t>0x18FF243B</t>
+  </si>
+  <si>
     <t>TWV1_P_RESP_ERROR</t>
   </si>
   <si>
@@ -3096,6 +3112,9 @@
   </si>
   <si>
     <t>Demand_Speed</t>
+  </si>
+  <si>
+    <t>0x18FF25EF</t>
   </si>
   <si>
     <t>VCU_TWV1_P_PosSet</t>
@@ -3803,10 +3822,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4647,37 +4666,37 @@
       <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <v>544</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>500</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>8</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>8</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>253</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L12" s="5"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="3">
@@ -21757,22 +21776,22 @@
         <v>15</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>242</v>
@@ -21797,7 +21816,7 @@
         <v>260</v>
       </c>
       <c r="Q136" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="137" ht="28" spans="1:17">
@@ -21808,22 +21827,22 @@
         <v>15</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F137" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="H137" s="3" t="s">
         <v>864</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>862</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>242</v>
@@ -21848,7 +21867,7 @@
         <v>261</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="138" ht="28" spans="1:17">
@@ -21859,22 +21878,22 @@
         <v>15</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>242</v>
@@ -21899,7 +21918,7 @@
         <v>262</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="139" ht="28" spans="1:17">
@@ -21910,22 +21929,22 @@
         <v>15</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>242</v>
@@ -21950,7 +21969,7 @@
         <v>263</v>
       </c>
       <c r="Q139" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="140" ht="28" spans="1:17">
@@ -21961,22 +21980,22 @@
         <v>15</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>242</v>
@@ -22001,7 +22020,7 @@
         <v>264</v>
       </c>
       <c r="Q140" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="141" ht="28" spans="1:17">
@@ -22012,22 +22031,22 @@
         <v>15</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>242</v>
@@ -22052,7 +22071,7 @@
         <v>265</v>
       </c>
       <c r="Q141" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="142" ht="28" spans="1:17">
@@ -22063,22 +22082,22 @@
         <v>15</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>242</v>
@@ -22103,7 +22122,7 @@
         <v>266</v>
       </c>
       <c r="Q142" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="143" ht="28" spans="1:17">
@@ -22114,22 +22133,22 @@
         <v>15</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>242</v>
@@ -22154,7 +22173,7 @@
         <v>267</v>
       </c>
       <c r="Q143" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="144" ht="70" spans="1:17">
@@ -22165,22 +22184,22 @@
         <v>15</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>143</v>
+        <v>860</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>238</v>
@@ -22195,7 +22214,7 @@
         <v>240</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="N144" s="3" t="s">
         <v>242</v>
@@ -22207,7 +22226,7 @@
         <v>268</v>
       </c>
       <c r="Q144" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="145" ht="56" spans="1:17">
@@ -22227,10 +22246,10 @@
         <v>19</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>462</v>
@@ -22258,7 +22277,7 @@
         <v>4</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="146" ht="28" spans="1:17">
@@ -22278,10 +22297,10 @@
         <v>19</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>462</v>
@@ -22309,7 +22328,7 @@
         <v>7</v>
       </c>
       <c r="Q146" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="147" ht="28" spans="1:17">
@@ -22329,10 +22348,10 @@
         <v>19</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>462</v>
@@ -22360,7 +22379,7 @@
         <v>8</v>
       </c>
       <c r="Q147" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="148" ht="28" spans="1:17">
@@ -22380,10 +22399,10 @@
         <v>19</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>462</v>
@@ -22411,7 +22430,7 @@
         <v>9</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="149" ht="28" spans="1:17">
@@ -22431,10 +22450,10 @@
         <v>19</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>462</v>
@@ -22462,7 +22481,7 @@
         <v>10</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -22482,10 +22501,10 @@
         <v>19</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>462</v>
@@ -22531,10 +22550,10 @@
         <v>94</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="H151" s="3" t="s">
         <v>462</v>
@@ -22580,10 +22599,10 @@
         <v>94</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>462</v>
@@ -22629,10 +22648,10 @@
         <v>94</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H153" s="3" t="s">
         <v>462</v>
@@ -22678,10 +22697,10 @@
         <v>94</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>462</v>
@@ -22727,10 +22746,10 @@
         <v>94</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>462</v>
@@ -22776,10 +22795,10 @@
         <v>94</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H156" s="3" t="s">
         <v>462</v>
@@ -22825,10 +22844,10 @@
         <v>94</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>462</v>
@@ -22846,7 +22865,7 @@
         <v>631</v>
       </c>
       <c r="M157" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="N157" s="3" t="s">
         <v>242</v>
@@ -22874,10 +22893,10 @@
         <v>94</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>462</v>
@@ -22923,10 +22942,10 @@
         <v>94</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>462</v>
@@ -22972,10 +22991,10 @@
         <v>94</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>462</v>
@@ -23021,10 +23040,10 @@
         <v>94</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>462</v>
@@ -23070,10 +23089,10 @@
         <v>94</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>462</v>
@@ -23119,10 +23138,10 @@
         <v>94</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>462</v>
@@ -23168,10 +23187,10 @@
         <v>94</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H164" s="3" t="s">
         <v>462</v>
@@ -23217,10 +23236,10 @@
         <v>94</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="H165" s="3" t="s">
         <v>462</v>
@@ -23266,10 +23285,10 @@
         <v>94</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>462</v>
@@ -23315,10 +23334,10 @@
         <v>94</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>462</v>
@@ -23336,7 +23355,7 @@
         <v>631</v>
       </c>
       <c r="M167" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="N167" s="3" t="s">
         <v>242</v>
@@ -23364,10 +23383,10 @@
         <v>94</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>462</v>
@@ -23413,10 +23432,10 @@
         <v>94</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>462</v>
@@ -23462,10 +23481,10 @@
         <v>94</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>462</v>
@@ -23511,10 +23530,10 @@
         <v>19</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>462</v>
@@ -23538,7 +23557,7 @@
         <v>137</v>
       </c>
       <c r="Q171" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -23558,10 +23577,10 @@
         <v>19</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>462</v>
@@ -23585,7 +23604,7 @@
         <v>138</v>
       </c>
       <c r="Q172" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -23605,10 +23624,10 @@
         <v>19</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>462</v>
@@ -23632,7 +23651,7 @@
         <v>139</v>
       </c>
       <c r="Q173" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="174" spans="1:17">
@@ -23652,10 +23671,10 @@
         <v>19</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="H174" s="3" t="s">
         <v>462</v>
@@ -23679,7 +23698,7 @@
         <v>140</v>
       </c>
       <c r="Q174" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="175" ht="56" spans="1:17">
@@ -23699,10 +23718,10 @@
         <v>19</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>462</v>
@@ -23750,10 +23769,10 @@
         <v>19</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>462</v>
@@ -23801,10 +23820,10 @@
         <v>19</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>462</v>
@@ -23852,10 +23871,10 @@
         <v>19</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>462</v>
@@ -23883,7 +23902,7 @@
         <v>167</v>
       </c>
       <c r="Q178" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="179" ht="56" spans="1:17">
@@ -23903,10 +23922,10 @@
         <v>19</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>462</v>
@@ -23954,7 +23973,7 @@
         <v>19</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>651</v>
@@ -24003,7 +24022,7 @@
         <v>94</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="3" t="s">
@@ -24046,7 +24065,7 @@
         <v>94</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="3" t="s">
@@ -24089,7 +24108,7 @@
         <v>94</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="3" t="s">
@@ -24112,7 +24131,7 @@
         <v>184</v>
       </c>
       <c r="Q183" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="184" ht="42" spans="1:17">
@@ -24132,7 +24151,7 @@
         <v>94</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="3" t="s">
@@ -24155,7 +24174,7 @@
         <v>185</v>
       </c>
       <c r="Q184" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="185" ht="28" spans="1:17">
@@ -24175,7 +24194,7 @@
         <v>94</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G185" s="3"/>
       <c r="H185" s="3" t="s">
@@ -24198,7 +24217,7 @@
         <v>186</v>
       </c>
       <c r="Q185" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="186" ht="28" spans="1:17">
@@ -24218,7 +24237,7 @@
         <v>94</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G186" s="3"/>
       <c r="H186" s="3" t="s">
@@ -24241,7 +24260,7 @@
         <v>187</v>
       </c>
       <c r="Q186" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="187" ht="28" spans="1:17">
@@ -24261,7 +24280,7 @@
         <v>94</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G187" s="3"/>
       <c r="H187" s="3" t="s">
@@ -24308,7 +24327,7 @@
         <v>94</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="3" t="s">
@@ -24355,7 +24374,7 @@
         <v>94</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="G189" s="3"/>
       <c r="H189" s="3" t="s">
@@ -24402,7 +24421,7 @@
         <v>94</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="G190" s="3"/>
       <c r="H190" s="3" t="s">
@@ -24449,7 +24468,7 @@
         <v>94</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="3" t="s">
@@ -24492,7 +24511,7 @@
         <v>94</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="G192" s="3"/>
       <c r="H192" s="3" t="s">
@@ -24535,7 +24554,7 @@
         <v>94</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="G193" s="3"/>
       <c r="H193" s="3" t="s">
@@ -24558,7 +24577,7 @@
         <v>221</v>
       </c>
       <c r="Q193" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="194" ht="42" spans="1:17">
@@ -24578,7 +24597,7 @@
         <v>94</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="3" t="s">
@@ -24601,7 +24620,7 @@
         <v>222</v>
       </c>
       <c r="Q194" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="195" ht="28" spans="1:17">
@@ -24621,7 +24640,7 @@
         <v>94</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="3" t="s">
@@ -24644,7 +24663,7 @@
         <v>223</v>
       </c>
       <c r="Q195" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="196" ht="28" spans="1:17">
@@ -24664,7 +24683,7 @@
         <v>94</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="3" t="s">
@@ -24687,7 +24706,7 @@
         <v>224</v>
       </c>
       <c r="Q196" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="197" ht="28" spans="1:17">
@@ -24707,7 +24726,7 @@
         <v>94</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="3" t="s">
@@ -24754,7 +24773,7 @@
         <v>94</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="3" t="s">
@@ -24801,7 +24820,7 @@
         <v>94</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="3" t="s">
@@ -24848,7 +24867,7 @@
         <v>94</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="G200" s="3"/>
       <c r="H200" s="3" t="s">
@@ -24889,19 +24908,19 @@
         <v>171</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>172</v>
+        <v>976</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>246</v>
@@ -24916,7 +24935,7 @@
         <v>240</v>
       </c>
       <c r="M201" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="N201" s="3" t="s">
         <v>242</v>
@@ -24928,7 +24947,7 @@
         <v>256</v>
       </c>
       <c r="Q201" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="202" ht="28" spans="1:17">
@@ -24942,19 +24961,19 @@
         <v>171</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>172</v>
+        <v>976</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>261</v>
@@ -24979,7 +24998,7 @@
         <v>257</v>
       </c>
       <c r="Q202" s="3" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
   </sheetData>
